--- a/Data/Csv/ItemData.xlsx
+++ b/Data/Csv/ItemData.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30117"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="46" documentId="11_31802F1733C7A0836B02CE998F682C9D7A7B838F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0939D968-3F94-46A1-8928-18535ACC7E0D}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project\Data\Csv\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC5E5876-FF45-4A41-B512-0B7F5A01FE34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
@@ -34,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="16">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -90,13 +93,22 @@
   </si>
   <si>
     <t>1000.0f</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>500.0f</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>2360.0f</t>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -109,6 +121,13 @@
       <color theme="1"/>
       <name val="游ゴシック"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -206,7 +225,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -502,10 +521,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -528,7 +547,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15.75">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -551,15 +570,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="15.75">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3" s="3">
         <v>0</v>
       </c>
       <c r="C3" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>11</v>
@@ -574,15 +593,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15.75">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B4" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>13</v>
@@ -597,7 +616,78 @@
         <v>8</v>
       </c>
     </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A5" s="3">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3">
+        <v>1</v>
+      </c>
+      <c r="C5" s="3">
+        <v>2</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A6" s="3">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3">
+        <v>1</v>
+      </c>
+      <c r="C6" s="3">
+        <v>2</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A7" s="3">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3">
+        <v>1</v>
+      </c>
+      <c r="C7" s="3">
+        <v>2</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Data/Csv/ItemData.xlsx
+++ b/Data/Csv/ItemData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project\Data\Csv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC5E5876-FF45-4A41-B512-0B7F5A01FE34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{531E719C-FA35-43D6-A7DE-77F1DF91F476}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="15">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -83,9 +83,6 @@
   </si>
   <si>
     <t>0.0f</t>
-  </si>
-  <si>
-    <t>500.0f</t>
   </si>
   <si>
     <t>800.0f</t>
@@ -581,10 +578,10 @@
         <v>1</v>
       </c>
       <c r="D3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>12</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>9</v>
@@ -630,7 +627,7 @@
         <v>13</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>9</v>
@@ -644,22 +641,22 @@
         <v>5</v>
       </c>
       <c r="B6" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.4">
@@ -667,22 +664,22 @@
         <v>6</v>
       </c>
       <c r="B7" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="F7" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F7" s="3" t="s">
-        <v>15</v>
-      </c>
       <c r="G7" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Csv/ItemData.xlsx
+++ b/Data/Csv/ItemData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project\Data\Csv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{531E719C-FA35-43D6-A7DE-77F1DF91F476}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D898ED9-39EA-40BA-BA3D-C3D8695508F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="10">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -76,19 +76,6 @@
     <t>100.0f</t>
   </si>
   <si>
-    <t>300.0f</t>
-  </si>
-  <si>
-    <t>2360.0f</t>
-  </si>
-  <si>
-    <t>0.0f</t>
-  </si>
-  <si>
-    <t>800.0f</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>1000.0f</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -96,15 +83,14 @@
     <t>500.0f</t>
     <phoneticPr fontId="2"/>
   </si>
-  <si>
-    <t>2360.0f</t>
-    <phoneticPr fontId="2"/>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="179" formatCode="0_ "/>
+  </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -193,7 +179,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -202,6 +188,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -518,7 +507,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.4">
@@ -557,14 +546,14 @@
       <c r="D2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>10</v>
+      <c r="E2" s="4">
+        <v>-547.22699999999998</v>
+      </c>
+      <c r="F2" s="3">
+        <v>2529.81</v>
+      </c>
+      <c r="G2" s="3">
+        <v>441.197</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.4">
@@ -580,14 +569,14 @@
       <c r="D3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>10</v>
+      <c r="E3" s="3">
+        <v>594.33900000000006</v>
+      </c>
+      <c r="F3" s="3">
+        <v>2502.5700000000002</v>
+      </c>
+      <c r="G3" s="3">
+        <v>524.47</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.4">
@@ -595,22 +584,22 @@
         <v>3</v>
       </c>
       <c r="B4" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="E4" s="3">
+        <v>728.40800000000002</v>
+      </c>
+      <c r="F4" s="3">
+        <v>2492.4699999999998</v>
+      </c>
+      <c r="G4" s="3">
+        <v>-388.41699999999997</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.4">
@@ -618,22 +607,22 @@
         <v>4</v>
       </c>
       <c r="B5" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="E5" s="3">
+        <v>-163.25200000000001</v>
+      </c>
+      <c r="F5" s="3">
+        <v>2463.69</v>
+      </c>
+      <c r="G5" s="3">
+        <v>-908.52599999999995</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.4">
@@ -641,22 +630,23 @@
         <v>5</v>
       </c>
       <c r="B6" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>13</v>
+        <v>7</v>
+      </c>
+      <c r="E6" s="3">
+        <v>-1104.3</v>
+      </c>
+      <c r="F6" s="3">
+        <v>2283.4</v>
+      </c>
+      <c r="G6" s="3">
+        <f>I8-675.71</f>
+        <v>-675.71</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.4">
@@ -664,22 +654,873 @@
         <v>6</v>
       </c>
       <c r="B7" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C7" s="3">
+        <v>1</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="3">
+        <v>486.95100000000002</v>
+      </c>
+      <c r="F7" s="3">
+        <v>2264.9899999999998</v>
+      </c>
+      <c r="G7" s="3">
+        <v>-1238.6199999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A8" s="3">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3">
+        <v>1</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="3">
+        <v>1501.08</v>
+      </c>
+      <c r="F8" s="3">
+        <v>2146.5</v>
+      </c>
+      <c r="G8" s="3">
+        <v>-229.601</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A9" s="3">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3">
+        <v>1</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" s="3">
+        <v>993.19500000000005</v>
+      </c>
+      <c r="F9" s="3">
+        <v>1982.76</v>
+      </c>
+      <c r="G9" s="3">
+        <v>1403.34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A10" s="3">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3">
+        <v>0</v>
+      </c>
+      <c r="C10" s="3">
+        <v>1</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" s="3">
+        <v>-298.01900000000001</v>
+      </c>
+      <c r="F10" s="3">
+        <v>2111.11</v>
+      </c>
+      <c r="G10" s="3">
+        <v>1537.45</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A11" s="3">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3">
+        <v>0</v>
+      </c>
+      <c r="C11" s="3">
+        <v>1</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="3">
+        <v>-1634.33</v>
+      </c>
+      <c r="F11" s="3">
+        <v>1977.92</v>
+      </c>
+      <c r="G11" s="3">
+        <v>540.28800000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A12" s="3">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3">
+        <v>1</v>
+      </c>
+      <c r="C12" s="3">
+        <v>2</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="3">
+        <v>-1766.17</v>
+      </c>
+      <c r="F12" s="3">
+        <v>1300.7</v>
+      </c>
+      <c r="G12" s="3">
+        <v>1428.11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A13" s="3">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3">
+        <v>1</v>
+      </c>
+      <c r="C13" s="3">
+        <v>2</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" s="3">
+        <v>-514.99099999999999</v>
+      </c>
+      <c r="F13" s="3">
+        <v>1192.5999999999999</v>
+      </c>
+      <c r="G13" s="3">
+        <v>2277.27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A14" s="3">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3">
+        <v>1</v>
+      </c>
+      <c r="C14" s="3">
+        <v>2</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14" s="3">
+        <v>1654.27</v>
+      </c>
+      <c r="F14" s="3">
+        <v>1225.1300000000001</v>
+      </c>
+      <c r="G14" s="3">
+        <v>1627.67</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A15" s="3">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3">
+        <v>1</v>
+      </c>
+      <c r="C15" s="3">
+        <v>2</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" s="3">
+        <v>1250.32</v>
+      </c>
+      <c r="F15" s="3">
+        <v>608.51300000000003</v>
+      </c>
+      <c r="G15" s="3">
+        <v>2219.7600000000002</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A16" s="3">
+        <v>15</v>
+      </c>
+      <c r="B16" s="3">
+        <v>1</v>
+      </c>
+      <c r="C16" s="3">
+        <v>2</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E16" s="3">
+        <v>2530.5100000000002</v>
+      </c>
+      <c r="F16" s="3">
+        <v>177.72300000000001</v>
+      </c>
+      <c r="G16" s="3">
+        <v>643.654</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A17" s="3">
+        <v>16</v>
+      </c>
+      <c r="B17" s="3">
+        <v>1</v>
+      </c>
+      <c r="C17" s="3">
+        <v>2</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E17" s="3">
+        <v>2416.39</v>
+      </c>
+      <c r="F17" s="3">
+        <v>981.61699999999996</v>
+      </c>
+      <c r="G17" s="3">
+        <v>-302.625</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A18" s="3">
+        <v>17</v>
+      </c>
+      <c r="B18" s="3">
+        <v>1</v>
+      </c>
+      <c r="C18" s="3">
+        <v>2</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E18" s="3">
+        <v>1701.94</v>
+      </c>
+      <c r="F18" s="3">
+        <v>162.47800000000001</v>
+      </c>
+      <c r="G18" s="3">
+        <v>-1979.66</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A19" s="3">
+        <v>18</v>
+      </c>
+      <c r="B19" s="3">
+        <v>1</v>
+      </c>
+      <c r="C19" s="3">
+        <v>2</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E19" s="3">
+        <v>243.161</v>
+      </c>
+      <c r="F19" s="3">
+        <v>1055.6199999999999</v>
+      </c>
+      <c r="G19" s="3">
+        <v>-2389.31</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A20" s="3">
+        <v>19</v>
+      </c>
+      <c r="B20" s="3">
+        <v>1</v>
+      </c>
+      <c r="C20" s="3">
+        <v>2</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-1522.5</v>
+      </c>
+      <c r="F20" s="3">
+        <v>219.52600000000001</v>
+      </c>
+      <c r="G20" s="3">
+        <v>-2119.7600000000002</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A21" s="3">
+        <v>20</v>
+      </c>
+      <c r="B21" s="3">
+        <v>1</v>
+      </c>
+      <c r="C21" s="3">
+        <v>2</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-2466.64</v>
+      </c>
+      <c r="F21" s="3">
+        <v>550.32799999999997</v>
+      </c>
+      <c r="G21" s="3">
+        <v>-704.30499999999995</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A22" s="3">
+        <v>21</v>
+      </c>
+      <c r="B22" s="3">
+        <v>1</v>
+      </c>
+      <c r="C22" s="3">
+        <v>2</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E22" s="3">
+        <v>-2498.29</v>
+      </c>
+      <c r="F22" s="3">
+        <v>618.53</v>
+      </c>
+      <c r="G22" s="3">
+        <v>528.51900000000001</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A23" s="3">
+        <v>22</v>
+      </c>
+      <c r="B23" s="3">
+        <v>1</v>
+      </c>
+      <c r="C23" s="3">
+        <v>2</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-1690.61</v>
+      </c>
+      <c r="F23" s="3">
+        <v>28.439</v>
+      </c>
+      <c r="G23" s="3">
+        <v>2005.86</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A24" s="3">
+        <v>23</v>
+      </c>
+      <c r="B24" s="3">
+        <v>1</v>
+      </c>
+      <c r="C24" s="3">
+        <v>2</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E24" s="3">
+        <v>-2605.4299999999998</v>
+      </c>
+      <c r="F24" s="3">
+        <v>15.247199999999999</v>
+      </c>
+      <c r="G24" s="3">
+        <v>321.93599999999998</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A25" s="3">
+        <v>24</v>
+      </c>
+      <c r="B25" s="3">
+        <v>1</v>
+      </c>
+      <c r="C25" s="3">
+        <v>2</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E25" s="3">
+        <v>-2621.0500000000002</v>
+      </c>
+      <c r="F25" s="3">
+        <v>-42.873199999999997</v>
+      </c>
+      <c r="G25" s="3">
+        <v>135.119</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A26" s="3">
+        <v>25</v>
+      </c>
+      <c r="B26" s="3">
+        <v>1</v>
+      </c>
+      <c r="C26" s="3">
+        <v>2</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E26" s="3">
+        <v>818.50800000000004</v>
+      </c>
+      <c r="F26" s="3">
+        <v>-59.340200000000003</v>
+      </c>
+      <c r="G26" s="3">
+        <v>2489.5700000000002</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A27" s="3">
+        <v>26</v>
+      </c>
+      <c r="B27" s="3">
+        <v>1</v>
+      </c>
+      <c r="C27" s="3">
+        <v>2</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-168.57300000000001</v>
+      </c>
+      <c r="F27" s="3">
+        <v>-465.99599999999998</v>
+      </c>
+      <c r="G27" s="3">
+        <v>2576.0100000000002</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A28" s="3">
+        <v>27</v>
+      </c>
+      <c r="B28" s="3">
+        <v>1</v>
+      </c>
+      <c r="C28" s="3">
+        <v>2</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E28" s="3">
+        <v>2473.0500000000002</v>
+      </c>
+      <c r="F28" s="3">
+        <v>-305.471</v>
+      </c>
+      <c r="G28" s="3">
+        <v>-789.89</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A29" s="3">
+        <v>28</v>
+      </c>
+      <c r="B29" s="3">
+        <v>1</v>
+      </c>
+      <c r="C29" s="3">
+        <v>2</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E29" s="3">
+        <v>2447.0500000000002</v>
+      </c>
+      <c r="F29" s="3">
+        <v>-640.34</v>
+      </c>
+      <c r="G29" s="3">
+        <v>674.19500000000005</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A30" s="3">
+        <v>29</v>
+      </c>
+      <c r="B30" s="3">
+        <v>1</v>
+      </c>
+      <c r="C30" s="3">
+        <v>2</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E30" s="3">
+        <v>376.12299999999999</v>
+      </c>
+      <c r="F30" s="3">
+        <v>-523.08799999999997</v>
+      </c>
+      <c r="G30" s="3">
+        <v>-2548.31</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A31" s="3">
+        <v>30</v>
+      </c>
+      <c r="B31" s="3">
+        <v>1</v>
+      </c>
+      <c r="C31" s="3">
+        <v>2</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E31" s="3">
+        <v>-1967.12</v>
+      </c>
+      <c r="F31" s="3">
+        <v>1341.56</v>
+      </c>
+      <c r="G31" s="3">
+        <v>-1091.98</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A32" s="3">
+        <v>31</v>
+      </c>
+      <c r="B32" s="3">
+        <v>2</v>
+      </c>
+      <c r="C32" s="3">
         <v>3</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>13</v>
+      <c r="D32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-642.40899999999999</v>
+      </c>
+      <c r="F32" s="3">
+        <v>-1884.94</v>
+      </c>
+      <c r="G32" s="3">
+        <v>1721.06</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A33" s="3">
+        <v>32</v>
+      </c>
+      <c r="B33" s="3">
+        <v>2</v>
+      </c>
+      <c r="C33" s="3">
+        <v>3</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="3">
+        <v>1197.5</v>
+      </c>
+      <c r="F33" s="3">
+        <v>-1667.39</v>
+      </c>
+      <c r="G33" s="3">
+        <v>1628.72</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A34" s="3">
+        <v>33</v>
+      </c>
+      <c r="B34" s="3">
+        <v>2</v>
+      </c>
+      <c r="C34" s="3">
+        <v>3</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E34" s="3">
+        <v>-1731.29</v>
+      </c>
+      <c r="F34" s="3">
+        <v>-1777.48</v>
+      </c>
+      <c r="G34" s="3">
+        <v>852.75099999999998</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A35" s="3">
+        <v>34</v>
+      </c>
+      <c r="B35" s="3">
+        <v>2</v>
+      </c>
+      <c r="C35" s="3">
+        <v>3</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-364.67500000000001</v>
+      </c>
+      <c r="F35" s="3">
+        <v>-2541.92</v>
+      </c>
+      <c r="G35" s="3">
+        <v>556.58299999999997</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A36" s="3">
+        <v>35</v>
+      </c>
+      <c r="B36" s="3">
+        <v>2</v>
+      </c>
+      <c r="C36" s="3">
+        <v>3</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" s="3">
+        <v>-1192.8800000000001</v>
+      </c>
+      <c r="F36" s="3">
+        <v>-2283.06</v>
+      </c>
+      <c r="G36" s="3">
+        <v>-510.976</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A37" s="3">
+        <v>36</v>
+      </c>
+      <c r="B37" s="3">
+        <v>2</v>
+      </c>
+      <c r="C37" s="3">
+        <v>3</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" s="3">
+        <v>-1763.13</v>
+      </c>
+      <c r="F37" s="3">
+        <v>-1469.39</v>
+      </c>
+      <c r="G37" s="3">
+        <v>-1288.82</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A38" s="3">
+        <v>37</v>
+      </c>
+      <c r="B38" s="3">
+        <v>2</v>
+      </c>
+      <c r="C38" s="3">
+        <v>3</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38" s="3">
+        <v>-724.54100000000005</v>
+      </c>
+      <c r="F38" s="3">
+        <v>-2020.35</v>
+      </c>
+      <c r="G38" s="3">
+        <v>-1505.46</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A39" s="3">
+        <v>38</v>
+      </c>
+      <c r="B39" s="3">
+        <v>2</v>
+      </c>
+      <c r="C39" s="3">
+        <v>3</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39" s="3">
+        <v>552.27099999999996</v>
+      </c>
+      <c r="F39" s="3">
+        <v>-2166.48</v>
+      </c>
+      <c r="G39" s="3">
+        <v>-1391.71</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A40" s="3">
+        <v>39</v>
+      </c>
+      <c r="B40" s="3">
+        <v>2</v>
+      </c>
+      <c r="C40" s="3">
+        <v>3</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="3">
+        <v>1445.31</v>
+      </c>
+      <c r="F40" s="3">
+        <v>-2013.62</v>
+      </c>
+      <c r="G40" s="3">
+        <v>-854.10299999999995</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A41" s="3">
+        <v>40</v>
+      </c>
+      <c r="B41" s="3">
+        <v>2</v>
+      </c>
+      <c r="C41" s="3">
+        <v>3</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="3">
+        <v>1414.7</v>
+      </c>
+      <c r="F41" s="3">
+        <v>-2214.85</v>
+      </c>
+      <c r="G41" s="3">
+        <v>120.92100000000001</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A42" s="3">
+        <v>41</v>
+      </c>
+      <c r="B42" s="3">
+        <v>2</v>
+      </c>
+      <c r="C42" s="3">
+        <v>3</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="3">
+        <v>1595.49</v>
+      </c>
+      <c r="F42" s="3">
+        <v>-1452.34</v>
+      </c>
+      <c r="G42" s="3">
+        <v>-1508.86</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A43" s="3">
+        <v>42</v>
+      </c>
+      <c r="B43" s="3">
+        <v>2</v>
+      </c>
+      <c r="C43" s="3">
+        <v>3</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="3">
+        <v>2130.61</v>
+      </c>
+      <c r="F43" s="3">
+        <v>-1522.22</v>
+      </c>
+      <c r="G43" s="3">
+        <v>-172.25</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A44" s="3">
+        <v>43</v>
+      </c>
+      <c r="B44" s="3">
+        <v>2</v>
+      </c>
+      <c r="C44" s="3">
+        <v>3</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="3">
+        <v>99.762200000000007</v>
+      </c>
+      <c r="F44" s="3">
+        <v>-2563.75</v>
+      </c>
+      <c r="G44" s="3">
+        <v>-584.28399999999999</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Csv/ItemData.xlsx
+++ b/Data/Csv/ItemData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project\Data\Csv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D898ED9-39EA-40BA-BA3D-C3D8695508F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5B25179F-00E5-4ACF-9FD2-11F633E5B9F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="11">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -83,13 +83,17 @@
     <t>500.0f</t>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <t>100.0f</t>
+    <phoneticPr fontId="2"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="179" formatCode="0_ "/>
+    <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -190,7 +194,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -544,16 +548,16 @@
         <v>1</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E2" s="4">
-        <v>-547.22699999999998</v>
+        <v>1522</v>
       </c>
       <c r="F2" s="3">
-        <v>2529.81</v>
+        <v>-244</v>
       </c>
       <c r="G2" s="3">
-        <v>441.197</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.4">
@@ -570,13 +574,13 @@
         <v>7</v>
       </c>
       <c r="E3" s="3">
-        <v>594.33900000000006</v>
+        <v>1362</v>
       </c>
       <c r="F3" s="3">
-        <v>2502.5700000000002</v>
+        <v>383</v>
       </c>
       <c r="G3" s="3">
-        <v>524.47</v>
+        <v>511</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.4">
@@ -593,13 +597,13 @@
         <v>7</v>
       </c>
       <c r="E4" s="3">
-        <v>728.40800000000002</v>
+        <v>1510</v>
       </c>
       <c r="F4" s="3">
-        <v>2492.4699999999998</v>
+        <v>-314</v>
       </c>
       <c r="G4" s="3">
-        <v>-388.41699999999997</v>
+        <v>582</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.4">
@@ -616,13 +620,13 @@
         <v>7</v>
       </c>
       <c r="E5" s="3">
-        <v>-163.25200000000001</v>
+        <v>1282</v>
       </c>
       <c r="F5" s="3">
-        <v>2463.69</v>
+        <v>336</v>
       </c>
       <c r="G5" s="3">
-        <v>-908.52599999999995</v>
+        <v>-855</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.4">
@@ -639,14 +643,13 @@
         <v>7</v>
       </c>
       <c r="E6" s="3">
-        <v>-1104.3</v>
+        <v>1399</v>
       </c>
       <c r="F6" s="3">
-        <v>2283.4</v>
+        <v>465</v>
       </c>
       <c r="G6" s="3">
-        <f>I8-675.71</f>
-        <v>-675.71</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.4">
@@ -663,13 +666,13 @@
         <v>7</v>
       </c>
       <c r="E7" s="3">
-        <v>486.95100000000002</v>
+        <v>1464</v>
       </c>
       <c r="F7" s="3">
-        <v>2264.9899999999998</v>
+        <v>-172</v>
       </c>
       <c r="G7" s="3">
-        <v>-1238.6199999999999</v>
+        <v>556</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.4">
@@ -686,13 +689,13 @@
         <v>7</v>
       </c>
       <c r="E8" s="3">
-        <v>1501.08</v>
+        <v>1250</v>
       </c>
       <c r="F8" s="3">
-        <v>2146.5</v>
+        <v>-578</v>
       </c>
       <c r="G8" s="3">
-        <v>-229.601</v>
+        <v>902</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.4">
@@ -709,13 +712,13 @@
         <v>7</v>
       </c>
       <c r="E9" s="3">
-        <v>993.19500000000005</v>
+        <v>1161</v>
       </c>
       <c r="F9" s="3">
-        <v>1982.76</v>
+        <v>134</v>
       </c>
       <c r="G9" s="3">
-        <v>1403.34</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.4">
@@ -732,13 +735,13 @@
         <v>7</v>
       </c>
       <c r="E10" s="3">
-        <v>-298.01900000000001</v>
+        <v>793</v>
       </c>
       <c r="F10" s="3">
-        <v>2111.11</v>
+        <v>514</v>
       </c>
       <c r="G10" s="3">
-        <v>1537.45</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.4">
@@ -755,13 +758,13 @@
         <v>7</v>
       </c>
       <c r="E11" s="3">
-        <v>-1634.33</v>
+        <v>1184</v>
       </c>
       <c r="F11" s="3">
-        <v>1977.92</v>
+        <v>686</v>
       </c>
       <c r="G11" s="3">
-        <v>540.28800000000001</v>
+        <v>919</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.4">
@@ -778,13 +781,13 @@
         <v>9</v>
       </c>
       <c r="E12" s="3">
-        <v>-1766.17</v>
+        <v>1440</v>
       </c>
       <c r="F12" s="3">
-        <v>1300.7</v>
+        <v>-701</v>
       </c>
       <c r="G12" s="3">
-        <v>1428.11</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.4">
@@ -801,13 +804,13 @@
         <v>9</v>
       </c>
       <c r="E13" s="3">
-        <v>-514.99099999999999</v>
+        <v>1117</v>
       </c>
       <c r="F13" s="3">
-        <v>1192.5999999999999</v>
+        <v>-935</v>
       </c>
       <c r="G13" s="3">
-        <v>2277.27</v>
+        <v>813</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.4">
@@ -824,13 +827,13 @@
         <v>9</v>
       </c>
       <c r="E14" s="3">
-        <v>1654.27</v>
+        <v>1059</v>
       </c>
       <c r="F14" s="3">
-        <v>1225.1300000000001</v>
+        <v>-169</v>
       </c>
       <c r="G14" s="3">
-        <v>1627.67</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.4">

--- a/Data/Csv/ItemData.xlsx
+++ b/Data/Csv/ItemData.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project\Data\Csv\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2416038\Desktop\GitHub\AGS2026_Summer\Data\Csv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EF38885-B894-4D3A-8A23-A0F0BAF15E79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14493752-CB41-4739-986B-F1E0D6250C59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -69,6 +69,13 @@
     <t>初期座標Z</t>
     <rPh sb="0" eb="4">
       <t>ショキザヒョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>大きさ</t>
+    <rPh sb="0" eb="1">
+      <t>オオ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -520,7 +527,9 @@
       <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2"/>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
@@ -530,24 +539,26 @@
         <v>1</v>
       </c>
       <c r="B2" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2" s="1">
         <v>1</v>
       </c>
       <c r="D2" s="1">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="E2" s="1">
-        <v>1423</v>
+        <v>39</v>
       </c>
       <c r="F2" s="1">
-        <v>226</v>
+        <v>0</v>
       </c>
       <c r="G2" s="1">
-        <v>-472</v>
-      </c>
-      <c r="H2" s="2"/>
+        <v>-6139</v>
+      </c>
+      <c r="H2" s="1">
+        <v>120</v>
+      </c>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
@@ -557,24 +568,26 @@
         <v>2</v>
       </c>
       <c r="B3" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C3" s="1">
         <v>1</v>
       </c>
       <c r="D3" s="1">
-        <v>100</v>
+        <v>350</v>
       </c>
       <c r="E3" s="1">
-        <v>1290</v>
+        <v>-955</v>
       </c>
       <c r="F3" s="1">
-        <v>-515</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1">
-        <v>-1026</v>
-      </c>
-      <c r="H3" s="2"/>
+        <v>-6176</v>
+      </c>
+      <c r="H3" s="1">
+        <v>120</v>
+      </c>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
@@ -584,24 +597,26 @@
         <v>3</v>
       </c>
       <c r="B4" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4" s="1">
         <v>1</v>
       </c>
       <c r="D4" s="1">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="E4" s="1">
-        <v>1163</v>
+        <v>-1865</v>
       </c>
       <c r="F4" s="1">
-        <v>-1168</v>
+        <v>0</v>
       </c>
       <c r="G4" s="1">
-        <v>105</v>
-      </c>
-      <c r="H4" s="2"/>
+        <v>-6719</v>
+      </c>
+      <c r="H4" s="1">
+        <v>120</v>
+      </c>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
@@ -611,24 +626,26 @@
         <v>4</v>
       </c>
       <c r="B5" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5" s="1">
         <v>1</v>
       </c>
       <c r="D5" s="1">
-        <v>100</v>
+        <v>350</v>
       </c>
       <c r="E5" s="1">
-        <v>986</v>
+        <v>-2492</v>
       </c>
       <c r="F5" s="1">
-        <v>-665</v>
+        <v>0</v>
       </c>
       <c r="G5" s="1">
-        <v>1376</v>
-      </c>
-      <c r="H5" s="2"/>
+        <v>-4265</v>
+      </c>
+      <c r="H5" s="1">
+        <v>120</v>
+      </c>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -638,24 +655,26 @@
         <v>5</v>
       </c>
       <c r="B6" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C6" s="1">
         <v>1</v>
       </c>
       <c r="D6" s="1">
-        <v>100</v>
+        <v>370</v>
       </c>
       <c r="E6" s="1">
-        <v>1231</v>
+        <v>2664</v>
       </c>
       <c r="F6" s="1">
-        <v>260</v>
+        <v>0</v>
       </c>
       <c r="G6" s="1">
-        <v>1009</v>
-      </c>
-      <c r="H6" s="2"/>
+        <v>-3865</v>
+      </c>
+      <c r="H6" s="1">
+        <v>120</v>
+      </c>
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
@@ -665,24 +684,26 @@
         <v>6</v>
       </c>
       <c r="B7" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C7" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7" s="1">
-        <v>500</v>
+        <v>420</v>
       </c>
       <c r="E7" s="1">
-        <v>166</v>
+        <v>-1345</v>
       </c>
       <c r="F7" s="1">
-        <v>-146</v>
+        <v>0</v>
       </c>
       <c r="G7" s="1">
-        <v>-1767</v>
-      </c>
-      <c r="H7" s="2"/>
+        <v>-2790</v>
+      </c>
+      <c r="H7" s="1">
+        <v>120</v>
+      </c>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
@@ -692,24 +713,26 @@
         <v>7</v>
       </c>
       <c r="B8" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C8" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8" s="1">
         <v>500</v>
       </c>
       <c r="E8" s="1">
-        <v>243</v>
+        <v>-5230</v>
       </c>
       <c r="F8" s="1">
-        <v>-1082</v>
+        <v>0</v>
       </c>
       <c r="G8" s="1">
-        <v>-1681</v>
-      </c>
-      <c r="H8" s="2"/>
+        <v>-3939</v>
+      </c>
+      <c r="H8" s="1">
+        <v>120</v>
+      </c>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
@@ -719,24 +742,26 @@
         <v>8</v>
       </c>
       <c r="B9" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C9" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9" s="1">
-        <v>400</v>
+        <v>550</v>
       </c>
       <c r="E9" s="1">
-        <v>-46</v>
+        <v>-4977</v>
       </c>
       <c r="F9" s="1">
-        <v>1284</v>
+        <v>0</v>
       </c>
       <c r="G9" s="1">
-        <v>-152</v>
-      </c>
-      <c r="H9" s="2"/>
+        <v>-2084</v>
+      </c>
+      <c r="H9" s="1">
+        <v>120</v>
+      </c>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
@@ -746,24 +771,26 @@
         <v>9</v>
       </c>
       <c r="B10" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C10" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D10" s="1">
-        <v>500</v>
+        <v>470</v>
       </c>
       <c r="E10" s="1">
-        <v>493</v>
+        <v>-4937</v>
       </c>
       <c r="F10" s="1">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="G10" s="1">
-        <v>-1001</v>
-      </c>
-      <c r="H10" s="2"/>
+        <v>-1117</v>
+      </c>
+      <c r="H10" s="1">
+        <v>120</v>
+      </c>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
@@ -773,24 +800,26 @@
         <v>10</v>
       </c>
       <c r="B11" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C11" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D11" s="1">
         <v>600</v>
       </c>
       <c r="E11" s="1">
-        <v>-484</v>
+        <v>-933</v>
       </c>
       <c r="F11" s="1">
-        <v>831</v>
+        <v>0</v>
       </c>
       <c r="G11" s="1">
-        <v>1638</v>
-      </c>
-      <c r="H11" s="2"/>
+        <v>-653</v>
+      </c>
+      <c r="H11" s="1">
+        <v>120</v>
+      </c>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
@@ -803,21 +832,23 @@
         <v>1</v>
       </c>
       <c r="C12" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D12" s="1">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="E12" s="1">
-        <v>-377</v>
+        <v>-2971</v>
       </c>
       <c r="F12" s="1">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="G12" s="1">
-        <v>1672</v>
-      </c>
-      <c r="H12" s="2"/>
+        <v>-400</v>
+      </c>
+      <c r="H12" s="1">
+        <v>120</v>
+      </c>
       <c r="I12" s="5"/>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
@@ -830,21 +861,23 @@
         <v>1</v>
       </c>
       <c r="C13" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D13" s="1">
-        <v>500</v>
+        <v>570</v>
       </c>
       <c r="E13" s="1">
-        <v>-72</v>
+        <v>2890</v>
       </c>
       <c r="F13" s="1">
-        <v>-1180</v>
+        <v>0</v>
       </c>
       <c r="G13" s="1">
-        <v>797</v>
-      </c>
-      <c r="H13" s="2"/>
+        <v>-1660</v>
+      </c>
+      <c r="H13" s="1">
+        <v>120</v>
+      </c>
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
@@ -857,21 +890,23 @@
         <v>1</v>
       </c>
       <c r="C14" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D14" s="1">
-        <v>400</v>
+        <v>550</v>
       </c>
       <c r="E14" s="1">
-        <v>51</v>
+        <v>940</v>
       </c>
       <c r="F14" s="1">
-        <v>-1820</v>
+        <v>0</v>
       </c>
       <c r="G14" s="1">
-        <v>-349</v>
-      </c>
-      <c r="H14" s="2"/>
+        <v>-2909</v>
+      </c>
+      <c r="H14" s="1">
+        <v>120</v>
+      </c>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
@@ -884,21 +919,23 @@
         <v>1</v>
       </c>
       <c r="C15" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15" s="1">
         <v>500</v>
       </c>
       <c r="E15" s="1">
-        <v>-161</v>
+        <v>1770</v>
       </c>
       <c r="F15" s="1">
-        <v>181</v>
+        <v>0</v>
       </c>
       <c r="G15" s="1">
-        <v>-603</v>
-      </c>
-      <c r="H15" s="2"/>
+        <v>-660</v>
+      </c>
+      <c r="H15" s="1">
+        <v>120</v>
+      </c>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
@@ -908,24 +945,26 @@
         <v>15</v>
       </c>
       <c r="B16" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C16" s="1">
         <v>2</v>
       </c>
       <c r="D16" s="1">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="E16" s="1">
-        <v>-1461</v>
+        <v>5013</v>
       </c>
       <c r="F16" s="1">
-        <v>434</v>
+        <v>0</v>
       </c>
       <c r="G16" s="1">
-        <v>879</v>
-      </c>
-      <c r="H16" s="2"/>
+        <v>1465</v>
+      </c>
+      <c r="H16" s="1">
+        <v>2</v>
+      </c>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
@@ -935,24 +974,26 @@
         <v>16</v>
       </c>
       <c r="B17" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C17" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D17" s="1">
-        <v>1800</v>
+        <v>1000</v>
       </c>
       <c r="E17" s="1">
-        <v>-842</v>
+        <v>2955</v>
       </c>
       <c r="F17" s="1">
-        <v>1047</v>
+        <v>0</v>
       </c>
       <c r="G17" s="1">
-        <v>1239</v>
-      </c>
-      <c r="H17" s="2"/>
+        <v>1349</v>
+      </c>
+      <c r="H17" s="1">
+        <v>2</v>
+      </c>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
@@ -962,24 +1003,26 @@
         <v>17</v>
       </c>
       <c r="B18" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D18" s="1">
-        <v>2000</v>
+        <v>1100</v>
       </c>
       <c r="E18" s="1">
-        <v>511</v>
+        <v>157</v>
       </c>
       <c r="F18" s="1">
-        <v>1299</v>
+        <v>0</v>
       </c>
       <c r="G18" s="1">
-        <v>232</v>
-      </c>
-      <c r="H18" s="2"/>
+        <v>1403</v>
+      </c>
+      <c r="H18" s="1">
+        <v>2</v>
+      </c>
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
       <c r="K18" s="2"/>
@@ -989,24 +1032,26 @@
         <v>18</v>
       </c>
       <c r="B19" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C19" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D19" s="1">
-        <v>1700</v>
+        <v>1000</v>
       </c>
       <c r="E19" s="1">
-        <v>-765</v>
+        <v>-2793</v>
       </c>
       <c r="F19" s="1">
-        <v>1365</v>
+        <v>0</v>
       </c>
       <c r="G19" s="1">
-        <v>408</v>
-      </c>
-      <c r="H19" s="2"/>
+        <v>1548</v>
+      </c>
+      <c r="H19" s="1">
+        <v>2</v>
+      </c>
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
@@ -1016,24 +1061,26 @@
         <v>19</v>
       </c>
       <c r="B20" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D20" s="1">
-        <v>2000</v>
+        <v>1200</v>
       </c>
       <c r="E20" s="1">
-        <v>-847</v>
+        <v>-3116</v>
       </c>
       <c r="F20" s="1">
-        <v>1126</v>
+        <v>0</v>
       </c>
       <c r="G20" s="1">
-        <v>-102</v>
-      </c>
-      <c r="H20" s="2"/>
+        <v>2808</v>
+      </c>
+      <c r="H20" s="1">
+        <v>2</v>
+      </c>
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
@@ -1043,45 +1090,107 @@
         <v>20</v>
       </c>
       <c r="B21" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C21" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D21" s="1">
-        <v>2100</v>
+        <v>1300</v>
       </c>
       <c r="E21" s="1">
-        <v>-477</v>
+        <v>804</v>
       </c>
       <c r="F21" s="1">
-        <v>880</v>
+        <v>0</v>
       </c>
       <c r="G21" s="1">
-        <v>-960</v>
-      </c>
-      <c r="H21" s="2"/>
+        <v>3568</v>
+      </c>
+      <c r="H21" s="1">
+        <v>2</v>
+      </c>
       <c r="I21" s="2"/>
       <c r="J21" s="2"/>
       <c r="K21" s="2"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1">
+        <v>0</v>
+      </c>
+      <c r="C22" s="1">
+        <v>2</v>
+      </c>
+      <c r="D22" s="1">
+        <v>1000</v>
+      </c>
+      <c r="E22" s="1">
+        <v>2843</v>
+      </c>
+      <c r="F22" s="1">
+        <v>0</v>
+      </c>
+      <c r="G22" s="1">
+        <v>3540</v>
+      </c>
+      <c r="H22" s="1">
+        <v>2</v>
+      </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A23" s="2"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
+      <c r="A23" s="1">
+        <v>22</v>
+      </c>
+      <c r="B23" s="1">
+        <v>0</v>
+      </c>
+      <c r="C23" s="1">
+        <v>2</v>
+      </c>
+      <c r="D23" s="1">
+        <v>1500</v>
+      </c>
+      <c r="E23" s="1">
+        <v>-1174</v>
+      </c>
+      <c r="F23" s="1">
+        <v>0</v>
+      </c>
+      <c r="G23" s="1">
+        <v>5811</v>
+      </c>
+      <c r="H23" s="1">
+        <v>2</v>
+      </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A24" s="2"/>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
+      <c r="A24" s="1">
+        <v>23</v>
+      </c>
+      <c r="B24" s="1">
+        <v>0</v>
+      </c>
+      <c r="C24" s="1">
+        <v>3</v>
+      </c>
+      <c r="D24" s="1">
+        <v>1600</v>
+      </c>
+      <c r="E24" s="1">
+        <v>-75</v>
+      </c>
+      <c r="F24" s="1">
+        <v>0</v>
+      </c>
+      <c r="G24" s="1">
+        <v>6094</v>
+      </c>
+      <c r="H24" s="1">
+        <v>2</v>
+      </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A25" s="2"/>
